--- a/outputs/14240.xlsx
+++ b/outputs/14240.xlsx
@@ -1588,7 +1588,7 @@
         <v>1</v>
       </c>
       <c r="U4" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R4)*($B$4:$B$75=$S4)*($C$3:$M$3=$T4)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R4)*($B$4:$B$75=S4)*($C$3:$M$3=T4)*$C$4:$M$75)</f>
         <v>1882</v>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
         <v>2</v>
       </c>
       <c r="U5" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R5)*($B$4:$B$75=$S5)*($C$3:$M$3=$T5)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R5)*($B$4:$B$75=S5)*($C$3:$M$3=T5)*$C$4:$M$75)</f>
         <v>2532</v>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
         <v>3</v>
       </c>
       <c r="U6" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R6)*($B$4:$B$75=$S6)*($C$3:$M$3=$T6)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R6)*($B$4:$B$75=S6)*($C$3:$M$3=T6)*$C$4:$M$75)</f>
         <v>3272</v>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
         <v>4</v>
       </c>
       <c r="U7" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R7)*($B$4:$B$75=$S7)*($C$3:$M$3=$T7)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R7)*($B$4:$B$75=S7)*($C$3:$M$3=T7)*$C$4:$M$75)</f>
         <v>5028</v>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
         <v>5</v>
       </c>
       <c r="U8" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R8)*($B$4:$B$75=$S8)*($C$3:$M$3=$T8)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R8)*($B$4:$B$75=S8)*($C$3:$M$3=T8)*$C$4:$M$75)</f>
         <v>7696</v>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
         <v>6</v>
       </c>
       <c r="U9" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R9)*($B$4:$B$75=$S9)*($C$3:$M$3=$T9)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R9)*($B$4:$B$75=S9)*($C$3:$M$3=T9)*$C$4:$M$75)</f>
         <v>8849</v>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>7</v>
       </c>
       <c r="U10" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R10)*($B$4:$B$75=$S10)*($C$3:$M$3=$T10)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R10)*($B$4:$B$75=S10)*($C$3:$M$3=T10)*$C$4:$M$75)</f>
         <v>10176</v>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
         <v>8</v>
       </c>
       <c r="U11" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R11)*($B$4:$B$75=$S11)*($C$3:$M$3=$T11)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R11)*($B$4:$B$75=S11)*($C$3:$M$3=T11)*$C$4:$M$75)</f>
         <v>12211</v>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
         <v>9</v>
       </c>
       <c r="U12" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R12)*($B$4:$B$75=$S12)*($C$3:$M$3=$T12)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R12)*($B$4:$B$75=S12)*($C$3:$M$3=T12)*$C$4:$M$75)</f>
         <v>14654</v>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="U13" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R13)*($B$4:$B$75=$S13)*($C$3:$M$3=$T13)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R13)*($B$4:$B$75=S13)*($C$3:$M$3=T13)*$C$4:$M$75)</f>
         <v>2338</v>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>2</v>
       </c>
       <c r="U14" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R14)*($B$4:$B$75=$S14)*($C$3:$M$3=$T14)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R14)*($B$4:$B$75=S14)*($C$3:$M$3=T14)*$C$4:$M$75)</f>
         <v>3283</v>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
         <v>3</v>
       </c>
       <c r="U15" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R15)*($B$4:$B$75=$S15)*($C$3:$M$3=$T15)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R15)*($B$4:$B$75=S15)*($C$3:$M$3=T15)*$C$4:$M$75)</f>
         <v>4309</v>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
         <v>4</v>
       </c>
       <c r="U16" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R16)*($B$4:$B$75=$S16)*($C$3:$M$3=$T16)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R16)*($B$4:$B$75=S16)*($C$3:$M$3=T16)*$C$4:$M$75)</f>
         <v>6703</v>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
         <v>5</v>
       </c>
       <c r="U17" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R17)*($B$4:$B$75=$S17)*($C$3:$M$3=$T17)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R17)*($B$4:$B$75=S17)*($C$3:$M$3=T17)*$C$4:$M$75)</f>
         <v>10260</v>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
         <v>6</v>
       </c>
       <c r="U18" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R18)*($B$4:$B$75=$S18)*($C$3:$M$3=$T18)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R18)*($B$4:$B$75=S18)*($C$3:$M$3=T18)*$C$4:$M$75)</f>
         <v>11800</v>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
         <v>7</v>
       </c>
       <c r="U19" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R19)*($B$4:$B$75=$S19)*($C$3:$M$3=$T19)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R19)*($B$4:$B$75=S19)*($C$3:$M$3=T19)*$C$4:$M$75)</f>
         <v>12980</v>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
         <v>8</v>
       </c>
       <c r="U20" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R20)*($B$4:$B$75=$S20)*($C$3:$M$3=$T20)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R20)*($B$4:$B$75=S20)*($C$3:$M$3=T20)*$C$4:$M$75)</f>
         <v>15576</v>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
         <v>9</v>
       </c>
       <c r="U21" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R21)*($B$4:$B$75=$S21)*($C$3:$M$3=$T21)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R21)*($B$4:$B$75=S21)*($C$3:$M$3=T21)*$C$4:$M$75)</f>
         <v>18692</v>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
         <v>1</v>
       </c>
       <c r="U22" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R22)*($B$4:$B$75=$S22)*($C$3:$M$3=$T22)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R22)*($B$4:$B$75=S22)*($C$3:$M$3=T22)*$C$4:$M$75)</f>
         <v>3306</v>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
         <v>2</v>
       </c>
       <c r="U23" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R23)*($B$4:$B$75=$S23)*($C$3:$M$3=$T23)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R23)*($B$4:$B$75=S23)*($C$3:$M$3=T23)*$C$4:$M$75)</f>
         <v>4430</v>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
         <v>3</v>
       </c>
       <c r="U24" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R24)*($B$4:$B$75=$S24)*($C$3:$M$3=$T24)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R24)*($B$4:$B$75=S24)*($C$3:$M$3=T24)*$C$4:$M$75)</f>
         <v>6065</v>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
         <v>4</v>
       </c>
       <c r="U25" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R25)*($B$4:$B$75=$S25)*($C$3:$M$3=$T25)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R25)*($B$4:$B$75=S25)*($C$3:$M$3=T25)*$C$4:$M$75)</f>
         <v>8380</v>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
         <v>5</v>
       </c>
       <c r="U26" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R26)*($B$4:$B$75=$S26)*($C$3:$M$3=$T26)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R26)*($B$4:$B$75=S26)*($C$3:$M$3=T26)*$C$4:$M$75)</f>
         <v>12826</v>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         <v>6</v>
       </c>
       <c r="U27" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R27)*($B$4:$B$75=$S27)*($C$3:$M$3=$T27)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R27)*($B$4:$B$75=S27)*($C$3:$M$3=T27)*$C$4:$M$75)</f>
         <v>14749</v>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
         <v>7</v>
       </c>
       <c r="U28" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R28)*($B$4:$B$75=$S28)*($C$3:$M$3=$T28)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R28)*($B$4:$B$75=S28)*($C$3:$M$3=T28)*$C$4:$M$75)</f>
         <v>16224</v>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
         <v>8</v>
       </c>
       <c r="U29" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R29)*($B$4:$B$75=$S29)*($C$3:$M$3=$T29)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R29)*($B$4:$B$75=S29)*($C$3:$M$3=T29)*$C$4:$M$75)</f>
         <v>19469</v>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
         <v>9</v>
       </c>
       <c r="U30" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R30)*($B$4:$B$75=$S30)*($C$3:$M$3=$T30)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R30)*($B$4:$B$75=S30)*($C$3:$M$3=T30)*$C$4:$M$75)</f>
         <v>23363</v>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
         <v>1</v>
       </c>
       <c r="U31" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R31)*($B$4:$B$75=$S31)*($C$3:$M$3=$T31)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R31)*($B$4:$B$75=S31)*($C$3:$M$3=T31)*$C$4:$M$75)</f>
         <v>4332</v>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
         <v>2</v>
       </c>
       <c r="U32" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R32)*($B$4:$B$75=$S32)*($C$3:$M$3=$T32)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R32)*($B$4:$B$75=S32)*($C$3:$M$3=T32)*$C$4:$M$75)</f>
         <v>5130</v>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
         <v>3</v>
       </c>
       <c r="U33" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R33)*($B$4:$B$75=$S33)*($C$3:$M$3=$T33)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R33)*($B$4:$B$75=S33)*($C$3:$M$3=T33)*$C$4:$M$75)</f>
         <v>7820</v>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
         <v>4</v>
       </c>
       <c r="U34" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R34)*($B$4:$B$75=$S34)*($C$3:$M$3=$T34)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R34)*($B$4:$B$75=S34)*($C$3:$M$3=T34)*$C$4:$M$75)</f>
         <v>12499</v>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
         <v>5</v>
       </c>
       <c r="U35" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R35)*($B$4:$B$75=$S35)*($C$3:$M$3=$T35)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R35)*($B$4:$B$75=S35)*($C$3:$M$3=T35)*$C$4:$M$75)</f>
         <v>14999</v>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
         <v>6</v>
       </c>
       <c r="U36" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R36)*($B$4:$B$75=$S36)*($C$3:$M$3=$T36)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R36)*($B$4:$B$75=S36)*($C$3:$M$3=T36)*$C$4:$M$75)</f>
         <v>17249</v>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
         <v>7</v>
       </c>
       <c r="U37" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R37)*($B$4:$B$75=$S37)*($C$3:$M$3=$T37)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R37)*($B$4:$B$75=S37)*($C$3:$M$3=T37)*$C$4:$M$75)</f>
         <v>19836</v>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
         <v>8</v>
       </c>
       <c r="U38" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R38)*($B$4:$B$75=$S38)*($C$3:$M$3=$T38)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R38)*($B$4:$B$75=S38)*($C$3:$M$3=T38)*$C$4:$M$75)</f>
         <v>23803</v>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
         <v>9</v>
       </c>
       <c r="U39" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R39)*($B$4:$B$75=$S39)*($C$3:$M$3=$T39)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R39)*($B$4:$B$75=S39)*($C$3:$M$3=T39)*$C$4:$M$75)</f>
         <v>28564</v>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
         <v>1</v>
       </c>
       <c r="U40" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R40)*($B$4:$B$75=$S40)*($C$3:$M$3=$T40)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R40)*($B$4:$B$75=S40)*($C$3:$M$3=T40)*$C$4:$M$75)</f>
         <v>5244</v>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
         <v>2</v>
       </c>
       <c r="U41" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R41)*($B$4:$B$75=$S41)*($C$3:$M$3=$T41)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R41)*($B$4:$B$75=S41)*($C$3:$M$3=T41)*$C$4:$M$75)</f>
         <v>6156</v>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
         <v>3</v>
       </c>
       <c r="U42" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R42)*($B$4:$B$75=$S42)*($C$3:$M$3=$T42)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R42)*($B$4:$B$75=S42)*($C$3:$M$3=T42)*$C$4:$M$75)</f>
         <v>9576</v>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
         <v>4</v>
       </c>
       <c r="U43" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R43)*($B$4:$B$75=$S43)*($C$3:$M$3=$T43)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R43)*($B$4:$B$75=S43)*($C$3:$M$3=T43)*$C$4:$M$75)</f>
         <v>15236</v>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
         <v>5</v>
       </c>
       <c r="U44" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R44)*($B$4:$B$75=$S44)*($C$3:$M$3=$T44)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R44)*($B$4:$B$75=S44)*($C$3:$M$3=T44)*$C$4:$M$75)</f>
         <v>17879</v>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
         <v>6</v>
       </c>
       <c r="U45" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R45)*($B$4:$B$75=$S45)*($C$3:$M$3=$T45)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R45)*($B$4:$B$75=S45)*($C$3:$M$3=T45)*$C$4:$M$75)</f>
         <v>20561</v>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
         <v>7</v>
       </c>
       <c r="U46" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R46)*($B$4:$B$75=$S46)*($C$3:$M$3=$T46)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R46)*($B$4:$B$75=S46)*($C$3:$M$3=T46)*$C$4:$M$75)</f>
         <v>22733</v>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
         <v>8</v>
       </c>
       <c r="U47" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R47)*($B$4:$B$75=$S47)*($C$3:$M$3=$T47)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R47)*($B$4:$B$75=S47)*($C$3:$M$3=T47)*$C$4:$M$75)</f>
         <v>27280</v>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
         <v>9</v>
       </c>
       <c r="U48" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R48)*($B$4:$B$75=$S48)*($C$3:$M$3=$T48)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R48)*($B$4:$B$75=S48)*($C$3:$M$3=T48)*$C$4:$M$75)</f>
         <v>32736</v>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
         <v>1</v>
       </c>
       <c r="U49" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R49)*($B$4:$B$75=$S49)*($C$3:$M$3=$T49)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R49)*($B$4:$B$75=S49)*($C$3:$M$3=T49)*$C$4:$M$75)</f>
         <v>6688</v>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
         <v>2</v>
       </c>
       <c r="U50" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R50)*($B$4:$B$75=$S50)*($C$3:$M$3=$T50)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R50)*($B$4:$B$75=S50)*($C$3:$M$3=T50)*$C$4:$M$75)</f>
         <v>8945</v>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
         <v>3</v>
       </c>
       <c r="U51" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R51)*($B$4:$B$75=$S51)*($C$3:$M$3=$T51)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R51)*($B$4:$B$75=S51)*($C$3:$M$3=T51)*$C$4:$M$75)</f>
         <v>11683</v>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
         <v>4</v>
       </c>
       <c r="U52" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R52)*($B$4:$B$75=$S52)*($C$3:$M$3=$T52)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R52)*($B$4:$B$75=S52)*($C$3:$M$3=T52)*$C$4:$M$75)</f>
         <v>18588</v>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
         <v>5</v>
       </c>
       <c r="U53" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R53)*($B$4:$B$75=$S53)*($C$3:$M$3=$T53)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R53)*($B$4:$B$75=S53)*($C$3:$M$3=T53)*$C$4:$M$75)</f>
         <v>21812</v>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
         <v>6</v>
       </c>
       <c r="U54" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R54)*($B$4:$B$75=$S54)*($C$3:$M$3=$T54)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R54)*($B$4:$B$75=S54)*($C$3:$M$3=T54)*$C$4:$M$75)</f>
         <v>25084</v>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
         <v>7</v>
       </c>
       <c r="U55" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R55)*($B$4:$B$75=$S55)*($C$3:$M$3=$T55)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R55)*($B$4:$B$75=S55)*($C$3:$M$3=T55)*$C$4:$M$75)</f>
         <v>27593</v>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
         <v>8</v>
       </c>
       <c r="U56" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R56)*($B$4:$B$75=$S56)*($C$3:$M$3=$T56)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R56)*($B$4:$B$75=S56)*($C$3:$M$3=T56)*$C$4:$M$75)</f>
         <v>33112</v>
       </c>
     </row>
@@ -4134,7 +4134,7 @@
         <v>9</v>
       </c>
       <c r="U57" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R57)*($B$4:$B$75=$S57)*($C$3:$M$3=$T57)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R57)*($B$4:$B$75=S57)*($C$3:$M$3=T57)*$C$4:$M$75)</f>
         <v>39734</v>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>1</v>
       </c>
       <c r="U58" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R58)*($B$4:$B$75=$S58)*($C$3:$M$3=$T58)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R58)*($B$4:$B$75=S58)*($C$3:$M$3=T58)*$C$4:$M$75)</f>
         <v>8160</v>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
         <v>2</v>
       </c>
       <c r="U59" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R59)*($B$4:$B$75=$S59)*($C$3:$M$3=$T59)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R59)*($B$4:$B$75=S59)*($C$3:$M$3=T59)*$C$4:$M$75)</f>
         <v>10913</v>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
         <v>3</v>
       </c>
       <c r="U60" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R60)*($B$4:$B$75=$S60)*($C$3:$M$3=$T60)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R60)*($B$4:$B$75=S60)*($C$3:$M$3=T60)*$C$4:$M$75)</f>
         <v>14252</v>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
         <v>4</v>
       </c>
       <c r="U61" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R61)*($B$4:$B$75=$S61)*($C$3:$M$3=$T61)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R61)*($B$4:$B$75=S61)*($C$3:$M$3=T61)*$C$4:$M$75)</f>
         <v>23708</v>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
         <v>5</v>
       </c>
       <c r="U62" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R62)*($B$4:$B$75=$S62)*($C$3:$M$3=$T62)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R62)*($B$4:$B$75=S62)*($C$3:$M$3=T62)*$C$4:$M$75)</f>
         <v>27820</v>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
         <v>6</v>
       </c>
       <c r="U63" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R63)*($B$4:$B$75=$S63)*($C$3:$M$3=$T63)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R63)*($B$4:$B$75=S63)*($C$3:$M$3=T63)*$C$4:$M$75)</f>
         <v>31993</v>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
         <v>7</v>
       </c>
       <c r="U64" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R64)*($B$4:$B$75=$S64)*($C$3:$M$3=$T64)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R64)*($B$4:$B$75=S64)*($C$3:$M$3=T64)*$C$4:$M$75)</f>
         <v>35193</v>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
         <v>8</v>
       </c>
       <c r="U65" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R65)*($B$4:$B$75=$S65)*($C$3:$M$3=$T65)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R65)*($B$4:$B$75=S65)*($C$3:$M$3=T65)*$C$4:$M$75)</f>
         <v>42232</v>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
         <v>9</v>
       </c>
       <c r="U66" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R66)*($B$4:$B$75=$S66)*($C$3:$M$3=$T66)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R66)*($B$4:$B$75=S66)*($C$3:$M$3=T66)*$C$4:$M$75)</f>
         <v>50678</v>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
         <v>1</v>
       </c>
       <c r="U67" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R67)*($B$4:$B$75=$S67)*($C$3:$M$3=$T67)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R67)*($B$4:$B$75=S67)*($C$3:$M$3=T67)*$C$4:$M$75)</f>
         <v>4332</v>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
         <v>2</v>
       </c>
       <c r="U68" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R68)*($B$4:$B$75=$S68)*($C$3:$M$3=$T68)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R68)*($B$4:$B$75=S68)*($C$3:$M$3=T68)*$C$4:$M$75)</f>
         <v>5130</v>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
         <v>3</v>
       </c>
       <c r="U69" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R69)*($B$4:$B$75=$S69)*($C$3:$M$3=$T69)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R69)*($B$4:$B$75=S69)*($C$3:$M$3=T69)*$C$4:$M$75)</f>
         <v>7820</v>
       </c>
     </row>
@@ -4498,7 +4498,7 @@
         <v>4</v>
       </c>
       <c r="U70" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R70)*($B$4:$B$75=$S70)*($C$3:$M$3=$T70)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R70)*($B$4:$B$75=S70)*($C$3:$M$3=T70)*$C$4:$M$75)</f>
         <v>12499</v>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
         <v>5</v>
       </c>
       <c r="U71" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R71)*($B$4:$B$75=$S71)*($C$3:$M$3=$T71)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R71)*($B$4:$B$75=S71)*($C$3:$M$3=T71)*$C$4:$M$75)</f>
         <v>14999</v>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
         <v>6</v>
       </c>
       <c r="U72" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R72)*($B$4:$B$75=$S72)*($C$3:$M$3=$T72)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R72)*($B$4:$B$75=S72)*($C$3:$M$3=T72)*$C$4:$M$75)</f>
         <v>17249</v>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
         <v>7</v>
       </c>
       <c r="U73" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R73)*($B$4:$B$75=$S73)*($C$3:$M$3=$T73)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R73)*($B$4:$B$75=S73)*($C$3:$M$3=T73)*$C$4:$M$75)</f>
         <v>19836</v>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
         <v>8</v>
       </c>
       <c r="U74" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R74)*($B$4:$B$75=$S74)*($C$3:$M$3=$T74)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R74)*($B$4:$B$75=S74)*($C$3:$M$3=T74)*$C$4:$M$75)</f>
         <v>23803</v>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="U75" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=$R75)*($B$4:$B$75=$S75)*($C$3:$M$3=$T75)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT(($A$4:$A$75=R75)*($B$4:$B$75=S75)*($C$3:$M$3=T75)*$C$4:$M$75)</f>
         <v>28564</v>
       </c>
     </row>

--- a/outputs/14240.xlsx
+++ b/outputs/14240.xlsx
@@ -1588,7 +1588,7 @@
         <v>1</v>
       </c>
       <c r="U4" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R4)*($B$4:$B$75=S4)*($C$3:$M$3=T4)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R4)*(B4:B75=S4)*(C3:M3=T4),C4:M75)</f>
         <v>1882</v>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
         <v>2</v>
       </c>
       <c r="U5" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R5)*($B$4:$B$75=S5)*($C$3:$M$3=T5)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R5)*(B4:B75=S5)*(C3:M3=T5),C4:M75)</f>
         <v>2532</v>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
         <v>3</v>
       </c>
       <c r="U6" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R6)*($B$4:$B$75=S6)*($C$3:$M$3=T6)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R6)*(B4:B75=S6)*(C3:M3=T6),C4:M75)</f>
         <v>3272</v>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
         <v>4</v>
       </c>
       <c r="U7" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R7)*($B$4:$B$75=S7)*($C$3:$M$3=T7)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R7)*(B4:B75=S7)*(C3:M3=T7),C4:M75)</f>
         <v>5028</v>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
         <v>5</v>
       </c>
       <c r="U8" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R8)*($B$4:$B$75=S8)*($C$3:$M$3=T8)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R8)*(B4:B75=S8)*(C3:M3=T8),C4:M75)</f>
         <v>7696</v>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
         <v>6</v>
       </c>
       <c r="U9" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R9)*($B$4:$B$75=S9)*($C$3:$M$3=T9)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R9)*(B4:B75=S9)*(C3:M3=T9),C4:M75)</f>
         <v>8849</v>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>7</v>
       </c>
       <c r="U10" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R10)*($B$4:$B$75=S10)*($C$3:$M$3=T10)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R10)*(B4:B75=S10)*(C3:M3=T10),C4:M75)</f>
         <v>10176</v>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
         <v>8</v>
       </c>
       <c r="U11" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R11)*($B$4:$B$75=S11)*($C$3:$M$3=T11)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R11)*(B4:B75=S11)*(C3:M3=T11),C4:M75)</f>
         <v>12211</v>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
         <v>9</v>
       </c>
       <c r="U12" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R12)*($B$4:$B$75=S12)*($C$3:$M$3=T12)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R12)*(B4:B75=S12)*(C3:M3=T12),C4:M75)</f>
         <v>14654</v>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="U13" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R13)*($B$4:$B$75=S13)*($C$3:$M$3=T13)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R13)*(B4:B75=S13)*(C3:M3=T13),C4:M75)</f>
         <v>2338</v>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>2</v>
       </c>
       <c r="U14" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R14)*($B$4:$B$75=S14)*($C$3:$M$3=T14)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R14)*(B4:B75=S14)*(C3:M3=T14),C4:M75)</f>
         <v>3283</v>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
         <v>3</v>
       </c>
       <c r="U15" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R15)*($B$4:$B$75=S15)*($C$3:$M$3=T15)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R15)*(B4:B75=S15)*(C3:M3=T15),C4:M75)</f>
         <v>4309</v>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
         <v>4</v>
       </c>
       <c r="U16" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R16)*($B$4:$B$75=S16)*($C$3:$M$3=T16)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R16)*(B4:B75=S16)*(C3:M3=T16),C4:M75)</f>
         <v>6703</v>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
         <v>5</v>
       </c>
       <c r="U17" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R17)*($B$4:$B$75=S17)*($C$3:$M$3=T17)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R17)*(B4:B75=S17)*(C3:M3=T17),C4:M75)</f>
         <v>10260</v>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
         <v>6</v>
       </c>
       <c r="U18" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R18)*($B$4:$B$75=S18)*($C$3:$M$3=T18)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R18)*(B4:B75=S18)*(C3:M3=T18),C4:M75)</f>
         <v>11800</v>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
         <v>7</v>
       </c>
       <c r="U19" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R19)*($B$4:$B$75=S19)*($C$3:$M$3=T19)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R19)*(B4:B75=S19)*(C3:M3=T19),C4:M75)</f>
         <v>12980</v>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
         <v>8</v>
       </c>
       <c r="U20" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R20)*($B$4:$B$75=S20)*($C$3:$M$3=T20)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R20)*(B4:B75=S20)*(C3:M3=T20),C4:M75)</f>
         <v>15576</v>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
         <v>9</v>
       </c>
       <c r="U21" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R21)*($B$4:$B$75=S21)*($C$3:$M$3=T21)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R21)*(B4:B75=S21)*(C3:M3=T21),C4:M75)</f>
         <v>18692</v>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
         <v>1</v>
       </c>
       <c r="U22" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R22)*($B$4:$B$75=S22)*($C$3:$M$3=T22)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R22)*(B4:B75=S22)*(C3:M3=T22),C4:M75)</f>
         <v>3306</v>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
         <v>2</v>
       </c>
       <c r="U23" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R23)*($B$4:$B$75=S23)*($C$3:$M$3=T23)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R23)*(B4:B75=S23)*(C3:M3=T23),C4:M75)</f>
         <v>4430</v>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
         <v>3</v>
       </c>
       <c r="U24" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R24)*($B$4:$B$75=S24)*($C$3:$M$3=T24)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R24)*(B4:B75=S24)*(C3:M3=T24),C4:M75)</f>
         <v>6065</v>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
         <v>4</v>
       </c>
       <c r="U25" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R25)*($B$4:$B$75=S25)*($C$3:$M$3=T25)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R25)*(B4:B75=S25)*(C3:M3=T25),C4:M75)</f>
         <v>8380</v>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
         <v>5</v>
       </c>
       <c r="U26" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R26)*($B$4:$B$75=S26)*($C$3:$M$3=T26)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R26)*(B4:B75=S26)*(C3:M3=T26),C4:M75)</f>
         <v>12826</v>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         <v>6</v>
       </c>
       <c r="U27" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R27)*($B$4:$B$75=S27)*($C$3:$M$3=T27)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R27)*(B4:B75=S27)*(C3:M3=T27),C4:M75)</f>
         <v>14749</v>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
         <v>7</v>
       </c>
       <c r="U28" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R28)*($B$4:$B$75=S28)*($C$3:$M$3=T28)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R28)*(B4:B75=S28)*(C3:M3=T28),C4:M75)</f>
         <v>16224</v>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
         <v>8</v>
       </c>
       <c r="U29" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R29)*($B$4:$B$75=S29)*($C$3:$M$3=T29)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R29)*(B4:B75=S29)*(C3:M3=T29),C4:M75)</f>
         <v>19469</v>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
         <v>9</v>
       </c>
       <c r="U30" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R30)*($B$4:$B$75=S30)*($C$3:$M$3=T30)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R30)*(B4:B75=S30)*(C3:M3=T30),C4:M75)</f>
         <v>23363</v>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
         <v>1</v>
       </c>
       <c r="U31" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R31)*($B$4:$B$75=S31)*($C$3:$M$3=T31)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R31)*(B4:B75=S31)*(C3:M3=T31),C4:M75)</f>
         <v>4332</v>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
         <v>2</v>
       </c>
       <c r="U32" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R32)*($B$4:$B$75=S32)*($C$3:$M$3=T32)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R32)*(B4:B75=S32)*(C3:M3=T32),C4:M75)</f>
         <v>5130</v>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
         <v>3</v>
       </c>
       <c r="U33" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R33)*($B$4:$B$75=S33)*($C$3:$M$3=T33)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R33)*(B4:B75=S33)*(C3:M3=T33),C4:M75)</f>
         <v>7820</v>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
         <v>4</v>
       </c>
       <c r="U34" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R34)*($B$4:$B$75=S34)*($C$3:$M$3=T34)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R34)*(B4:B75=S34)*(C3:M3=T34),C4:M75)</f>
         <v>12499</v>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
         <v>5</v>
       </c>
       <c r="U35" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R35)*($B$4:$B$75=S35)*($C$3:$M$3=T35)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R35)*(B4:B75=S35)*(C3:M3=T35),C4:M75)</f>
         <v>14999</v>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
         <v>6</v>
       </c>
       <c r="U36" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R36)*($B$4:$B$75=S36)*($C$3:$M$3=T36)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R36)*(B4:B75=S36)*(C3:M3=T36),C4:M75)</f>
         <v>17249</v>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
         <v>7</v>
       </c>
       <c r="U37" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R37)*($B$4:$B$75=S37)*($C$3:$M$3=T37)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R37)*(B4:B75=S37)*(C3:M3=T37),C4:M75)</f>
         <v>19836</v>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
         <v>8</v>
       </c>
       <c r="U38" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R38)*($B$4:$B$75=S38)*($C$3:$M$3=T38)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R38)*(B4:B75=S38)*(C3:M3=T38),C4:M75)</f>
         <v>23803</v>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
         <v>9</v>
       </c>
       <c r="U39" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R39)*($B$4:$B$75=S39)*($C$3:$M$3=T39)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R39)*(B4:B75=S39)*(C3:M3=T39),C4:M75)</f>
         <v>28564</v>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
         <v>1</v>
       </c>
       <c r="U40" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R40)*($B$4:$B$75=S40)*($C$3:$M$3=T40)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R40)*(B4:B75=S40)*(C3:M3=T40),C4:M75)</f>
         <v>5244</v>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
         <v>2</v>
       </c>
       <c r="U41" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R41)*($B$4:$B$75=S41)*($C$3:$M$3=T41)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R41)*(B4:B75=S41)*(C3:M3=T41),C4:M75)</f>
         <v>6156</v>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
         <v>3</v>
       </c>
       <c r="U42" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R42)*($B$4:$B$75=S42)*($C$3:$M$3=T42)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R42)*(B4:B75=S42)*(C3:M3=T42),C4:M75)</f>
         <v>9576</v>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
         <v>4</v>
       </c>
       <c r="U43" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R43)*($B$4:$B$75=S43)*($C$3:$M$3=T43)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R43)*(B4:B75=S43)*(C3:M3=T43),C4:M75)</f>
         <v>15236</v>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
         <v>5</v>
       </c>
       <c r="U44" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R44)*($B$4:$B$75=S44)*($C$3:$M$3=T44)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R44)*(B4:B75=S44)*(C3:M3=T44),C4:M75)</f>
         <v>17879</v>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
         <v>6</v>
       </c>
       <c r="U45" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R45)*($B$4:$B$75=S45)*($C$3:$M$3=T45)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R45)*(B4:B75=S45)*(C3:M3=T45),C4:M75)</f>
         <v>20561</v>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
         <v>7</v>
       </c>
       <c r="U46" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R46)*($B$4:$B$75=S46)*($C$3:$M$3=T46)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R46)*(B4:B75=S46)*(C3:M3=T46),C4:M75)</f>
         <v>22733</v>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
         <v>8</v>
       </c>
       <c r="U47" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R47)*($B$4:$B$75=S47)*($C$3:$M$3=T47)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R47)*(B4:B75=S47)*(C3:M3=T47),C4:M75)</f>
         <v>27280</v>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
         <v>9</v>
       </c>
       <c r="U48" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R48)*($B$4:$B$75=S48)*($C$3:$M$3=T48)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R48)*(B4:B75=S48)*(C3:M3=T48),C4:M75)</f>
         <v>32736</v>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
         <v>1</v>
       </c>
       <c r="U49" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R49)*($B$4:$B$75=S49)*($C$3:$M$3=T49)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R49)*(B4:B75=S49)*(C3:M3=T49),C4:M75)</f>
         <v>6688</v>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
         <v>2</v>
       </c>
       <c r="U50" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R50)*($B$4:$B$75=S50)*($C$3:$M$3=T50)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R50)*(B4:B75=S50)*(C3:M3=T50),C4:M75)</f>
         <v>8945</v>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
         <v>3</v>
       </c>
       <c r="U51" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R51)*($B$4:$B$75=S51)*($C$3:$M$3=T51)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R51)*(B4:B75=S51)*(C3:M3=T51),C4:M75)</f>
         <v>11683</v>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
         <v>4</v>
       </c>
       <c r="U52" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R52)*($B$4:$B$75=S52)*($C$3:$M$3=T52)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R52)*(B4:B75=S52)*(C3:M3=T52),C4:M75)</f>
         <v>18588</v>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
         <v>5</v>
       </c>
       <c r="U53" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R53)*($B$4:$B$75=S53)*($C$3:$M$3=T53)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R53)*(B4:B75=S53)*(C3:M3=T53),C4:M75)</f>
         <v>21812</v>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
         <v>6</v>
       </c>
       <c r="U54" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R54)*($B$4:$B$75=S54)*($C$3:$M$3=T54)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R54)*(B4:B75=S54)*(C3:M3=T54),C4:M75)</f>
         <v>25084</v>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
         <v>7</v>
       </c>
       <c r="U55" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R55)*($B$4:$B$75=S55)*($C$3:$M$3=T55)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R55)*(B4:B75=S55)*(C3:M3=T55),C4:M75)</f>
         <v>27593</v>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
         <v>8</v>
       </c>
       <c r="U56" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R56)*($B$4:$B$75=S56)*($C$3:$M$3=T56)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R56)*(B4:B75=S56)*(C3:M3=T56),C4:M75)</f>
         <v>33112</v>
       </c>
     </row>
@@ -4134,7 +4134,7 @@
         <v>9</v>
       </c>
       <c r="U57" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R57)*($B$4:$B$75=S57)*($C$3:$M$3=T57)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R57)*(B4:B75=S57)*(C3:M3=T57),C4:M75)</f>
         <v>39734</v>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>1</v>
       </c>
       <c r="U58" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R58)*($B$4:$B$75=S58)*($C$3:$M$3=T58)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R58)*(B4:B75=S58)*(C3:M3=T58),C4:M75)</f>
         <v>8160</v>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
         <v>2</v>
       </c>
       <c r="U59" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R59)*($B$4:$B$75=S59)*($C$3:$M$3=T59)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R59)*(B4:B75=S59)*(C3:M3=T59),C4:M75)</f>
         <v>10913</v>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
         <v>3</v>
       </c>
       <c r="U60" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R60)*($B$4:$B$75=S60)*($C$3:$M$3=T60)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R60)*(B4:B75=S60)*(C3:M3=T60),C4:M75)</f>
         <v>14252</v>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
         <v>4</v>
       </c>
       <c r="U61" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R61)*($B$4:$B$75=S61)*($C$3:$M$3=T61)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R61)*(B4:B75=S61)*(C3:M3=T61),C4:M75)</f>
         <v>23708</v>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
         <v>5</v>
       </c>
       <c r="U62" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R62)*($B$4:$B$75=S62)*($C$3:$M$3=T62)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R62)*(B4:B75=S62)*(C3:M3=T62),C4:M75)</f>
         <v>27820</v>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
         <v>6</v>
       </c>
       <c r="U63" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R63)*($B$4:$B$75=S63)*($C$3:$M$3=T63)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R63)*(B4:B75=S63)*(C3:M3=T63),C4:M75)</f>
         <v>31993</v>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
         <v>7</v>
       </c>
       <c r="U64" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R64)*($B$4:$B$75=S64)*($C$3:$M$3=T64)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R64)*(B4:B75=S64)*(C3:M3=T64),C4:M75)</f>
         <v>35193</v>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
         <v>8</v>
       </c>
       <c r="U65" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R65)*($B$4:$B$75=S65)*($C$3:$M$3=T65)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R65)*(B4:B75=S65)*(C3:M3=T65),C4:M75)</f>
         <v>42232</v>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
         <v>9</v>
       </c>
       <c r="U66" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R66)*($B$4:$B$75=S66)*($C$3:$M$3=T66)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R66)*(B4:B75=S66)*(C3:M3=T66),C4:M75)</f>
         <v>50678</v>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
         <v>1</v>
       </c>
       <c r="U67" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R67)*($B$4:$B$75=S67)*($C$3:$M$3=T67)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R67)*(B4:B75=S67)*(C3:M3=T67),C4:M75)</f>
         <v>4332</v>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
         <v>2</v>
       </c>
       <c r="U68" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R68)*($B$4:$B$75=S68)*($C$3:$M$3=T68)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R68)*(B4:B75=S68)*(C3:M3=T68),C4:M75)</f>
         <v>5130</v>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
         <v>3</v>
       </c>
       <c r="U69" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R69)*($B$4:$B$75=S69)*($C$3:$M$3=T69)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R69)*(B4:B75=S69)*(C3:M3=T69),C4:M75)</f>
         <v>7820</v>
       </c>
     </row>
@@ -4498,7 +4498,7 @@
         <v>4</v>
       </c>
       <c r="U70" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R70)*($B$4:$B$75=S70)*($C$3:$M$3=T70)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R70)*(B4:B75=S70)*(C3:M3=T70),C4:M75)</f>
         <v>12499</v>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
         <v>5</v>
       </c>
       <c r="U71" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R71)*($B$4:$B$75=S71)*($C$3:$M$3=T71)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R71)*(B4:B75=S71)*(C3:M3=T71),C4:M75)</f>
         <v>14999</v>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
         <v>6</v>
       </c>
       <c r="U72" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R72)*($B$4:$B$75=S72)*($C$3:$M$3=T72)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R72)*(B4:B75=S72)*(C3:M3=T72),C4:M75)</f>
         <v>17249</v>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
         <v>7</v>
       </c>
       <c r="U73" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R73)*($B$4:$B$75=S73)*($C$3:$M$3=T73)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R73)*(B4:B75=S73)*(C3:M3=T73),C4:M75)</f>
         <v>19836</v>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
         <v>8</v>
       </c>
       <c r="U74" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R74)*($B$4:$B$75=S74)*($C$3:$M$3=T74)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R74)*(B4:B75=S74)*(C3:M3=T74),C4:M75)</f>
         <v>23803</v>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="U75" s="2" t="n">
-        <f aca="false">SUMPRODUCT(($A$4:$A$75=R75)*($B$4:$B$75=S75)*($C$3:$M$3=T75)*$C$4:$M$75)</f>
+        <f aca="false">SUMPRODUCT((A4:A75=R75)*(B4:B75=S75)*(C3:M3=T75),C4:M75)</f>
         <v>28564</v>
       </c>
     </row>
